--- a/prisma/AUTHOR_CONTACT_LOG_GENERADO.xlsx
+++ b/prisma/AUTHOR_CONTACT_LOG_GENERADO.xlsx
@@ -586,13 +586,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Revisión: Identificación Granular de Intenciones Comunicativas en Publicaciones Digitales (2020-2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
+          <t>Revisión: Identificación Granular de Intenciones Comunicativas en Publicaciones Digitales (2021-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -608,7 +606,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Artículos elegibles (Etapa 2, relevancia ≥ 0.40) no disponibles vía Sci-Hub, UNPAYWALL, ni acceso institucional INACAP</t>
+          <t>Artículos elegibles en la Etapa 2 (método + intención + año ≥ 2021) cuyo texto completo no pudo obtenerse mediante APIs de acceso abierto (Unpaywall, CORE, arXiv, Europe PMC) ni acceso institucional</t>
         </is>
       </c>
     </row>
@@ -632,7 +630,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Mayo–Junio 2025</t>
+          <t>Junio de 2026 (recolección de correos el 3–4 de junio; fechas de envío por confirmar)</t>
         </is>
       </c>
     </row>
@@ -656,13 +654,11 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>0 PDFs obtenidos por esta vía (acceso restringido o sin respuesta); corpus final basado en PDFs disponibles (n=549)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
+          <t>El registro no documenta respuestas con PDF adjunto (por confirmar por el autor). Del total de 643 elegibles se obtuvo texto completo de 549; 94 no pudieron obtenerse</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -728,7 +724,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>De articulos_no_descargados_con_emails.json</t>
+          <t>De articulos_no_descargados_con_emails.json. Estado al 3–4 de junio de 2026; el cierre final fue de 94 no obtenidos</t>
         </is>
       </c>
     </row>
@@ -828,7 +824,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Obtenidos vía Sci-Hub, ResearchGate, UNPAYWALL o acceso institucional</t>
+          <t>Obtenidos por APIs de acceso abierto, acceso institucional y descarga manual</t>
         </is>
       </c>
     </row>
@@ -9363,17 +9359,17 @@
     <row r="2" ht="50" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>2025-04-15 al 2025-04-30</t>
+          <t>2026-04-28 al 2026-05-04</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Identificación de artículos elegibles sin texto completo</t>
+          <t>Cribado de metadatos (Etapa 2) y lista de elegibles</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>373 artículos elegibles en Etapa 2; 549 con PDF disponible</t>
+          <t>643 elegibles (método + intención + año ≥ 2021)</t>
         </is>
       </c>
       <c r="D2" s="15" t="inlineStr">
@@ -9383,68 +9379,68 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Pipeline LLM Etapa 2 completado; gap de ~190 artículos sin PDF</t>
+          <t>Lista de elegibles generada el 4 de mayo de 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="50" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>2025-05-01 al 2025-05-10</t>
+          <t>2026-05-04 al 2026-05-06</t>
         </is>
       </c>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t>Intento de descarga masiva (Sci-Hub, UNPAYWALL)</t>
+          <t>Descarga automática por APIs y vías alternativas</t>
         </is>
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>Sci-Hub bloqueado en red; 0/50 en open access según UNPAYWALL</t>
+          <t>Resultados en descargas_log.json; sin cifra consolidada en este registro</t>
         </is>
       </c>
       <c r="D3" s="22" t="inlineStr">
         <is>
-          <t>50 artículos probados</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E3" s="21" t="inlineStr">
         <is>
-          <t>Scripts: descargar_unpaywall.py, descargar_articulos.py</t>
+          <t>Scripts: descargar_*.py</t>
         </is>
       </c>
     </row>
     <row r="4" ht="50" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>2025-05-11 al 2025-05-20</t>
+          <t>2026-06-03 al 2026-06-04</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Extracción de emails de autores correspondientes</t>
+          <t>Descarga manual y recolección de correos de autores</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>140 emails identificados (placeholders — búsqueda manual requerida)</t>
+          <t>Unos 138 artículos pendientes de descarga</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>140 artículos</t>
+          <t>140 artículos con contacto</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Scripts: email_template.py; fuentes: ResearchGate, Academia.edu, Scholar</t>
+          <t>Fuente de correos: ResearchGate, Academia.edu, Google Scholar</t>
         </is>
       </c>
     </row>
     <row r="5" ht="50" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
-          <t>2025-05-21 al 2025-06-05</t>
+          <t>Junio de 2026 (fechas por confirmar)</t>
         </is>
       </c>
       <c r="B5" s="21" t="inlineStr">
@@ -9454,7 +9450,7 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>Envíos realizados para los contactos disponibles; sin respuestas recibidas</t>
+          <t>Sin respuestas confirmadas en los registros del pipeline</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -9464,14 +9460,14 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>Plantilla formal de solicitud de manuscrito para revisión académica</t>
+          <t>Plantilla formal de solicitud de manuscrito</t>
         </is>
       </c>
     </row>
     <row r="6" ht="50" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>2025-06-06 al 2025-06-20</t>
+          <t>Por confirmar</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -9481,7 +9477,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Sin respuestas confirmadas en registros del pipeline</t>
+          <t>Sin respuestas confirmadas en los registros del pipeline</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
@@ -9491,51 +9487,51 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Segunda ronda de contacto; proceso documentado en este log</t>
+          <t>Verificar fechas contra el correo del autor</t>
         </is>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1">
       <c r="A7" s="21" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2026-07-12 al 2026-07-24</t>
         </is>
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>Cierre del proceso de contacto</t>
+          <t>Análisis de texto completo (Etapa 3)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>0 PDFs obtenidos por vía de contacto a autores</t>
+          <t>549 con texto completo; 94 no obtenidos</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>549 artículos</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>Corpus final: 549 artículos con PDF (obtenidos por otras vías). Etapa 3 completada.</t>
+          <t>Cierre de la obtención de texto completo</t>
         </is>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>2025-07 en adelante</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Acceso institucional INACAP (ACM, IEEE Xplore)</t>
+          <t>Cronología parcialmente verificada</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Alternativa para futuros estudios; no implementada en esta RSL</t>
+          <t>Las fechas marcadas "por confirmar" deben contrastarse con el correo del autor antes de depositar este registro</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
@@ -9545,7 +9541,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Solución identificada pero fuera del alcance temporal de la revisión</t>
+          <t>—</t>
         </is>
       </c>
     </row>
